--- a/data/vacancies.xlsx
+++ b/data/vacancies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,6 +660,1298 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>128979005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Backend-разработчик (Python)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128979005</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Опыт разработки backend-сервисов и API. Знание одного или нескольких фреймворков: Django / Flask / FastAPI. Понимание принципов REST. Опыт работы с... Разрабатывать и поддерживать серверную часть приложений. Проектировать и реализовывать API для frontend-клиентов и внешних систем. Реализовывать бизнес-логику и...</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>129013159</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Младший аналитик (Python)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/129013159</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Внимательность к деталям, инициативность. Уверенный уровень владения Python. Базовый уровень владения SQL. Навыки владения Linux, Docker являются преимуществом. Разработка Python-скриптов для получения данных с маркетплейсов: Сбор и обновление статистики из личных кабинетов селлеров через REST API и...</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>128953827</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Python developer - FastAPI, Django</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128953827</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Какие знания и опыт мы ожидаем? Уверенное знание Python 10 и фреймворков Django DRF и FastAPI. Опыт проектирование API в... Придется разбираться с существующими сервисами, решениями и писать. Новые, используя имеющие наработки. Разрабатывать и нести ответственность за архитектуру решения. </t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>128944115</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Python-разработчик (фитнес-клуб)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128944115</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Что ты будешь делать: — Знание Python и базовых принципов веб-разработки. — Опыт работы (или учебных проектов) с Django или FastAPI. —  Разрабатывать и поддерживать внутренние и клиентские веб-сервисы на Python (Django/FastAPI). — Работать над API для мобильного приложения и сайта. — </t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>128960677</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>270000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>340000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128960677</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Уверенное владение от Python 3.8+. Опыт работы с CУБД (MySQL\Postgres\Mongo). Опыт работы с Redis.  Разработка асинхронной микросервисной архитектуры на FastAPI. Высокие требования к отказоустойчивости платформы. Тесное взаимодействие с командами тестирования и аналитики.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>128872507</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Backend-разработчик (Python / FastAPI)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128872507</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>...года с Python и 1+ год с FastAPI (или aiohttp/Starlette). Уверенное владение стеком: FastAPI, Uvicorn, Python 3.10... Разрабатывать и масштабировать бэкенд на FastAPI и Python 3.10+. Проектировать и реализовывать API для работы с данными компаний...</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>128762692</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Backend-разработчик (Python, Junior–Middle)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128762692</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опыт коммерческой разработки (или уверенные pet-проекты). Хорошее знание Python. Опыт разработки REST API (FastAPI / Flask / Django REST).  Платформа создаётся с нуля, под реальные задачи: диагностика знаний, работа с учебными заданиями, личные кабинеты, аналитика, интеграция AI-инструментов. </t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>128958487</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Python Developer (Middle+)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128958487</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опыт коммерческой разработки на Python от 3 лет. Уверенные знания FastApi. Python 3.7. Уверенное владение Django или Django 5... Разработка и поддержка приложения на базе FastApi. Проектирование сервисов обработки сообщений RabbitMQ. Проектирование и оптимизация баз данных PostgreSQL. </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>125145422</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Middle Python разработчик</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/125145422</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Широкий опыт разработки на Python (3.x) от 3 лет. Опыт проектирования высоконагруженных сервисов. Уверенное знание и применение асинхронных фреймворков... Развивать и поддерживать платформу распознавания лиц. Проектировать API и архитектуру для новых задач и сервисов. Делать проект лучше со всех...</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>128010882</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Инженер-программист (python)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128010882</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Опыт программирования встраиваемых микропроцессоров. Опыт работы с системой контроля версий (SVN, GIT и им подобных). Знание языка python. Участие в разработке алгоритмов работы навигационной аппаратуры с целью комплексирования различных навигационных датчиков, повышения достоверности навигационных определений, чувствительности и помехоустойчивости...</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>87838855</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Разработчик Python</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>287000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/87838855</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Опыт разработки на Python 3.6+ от 3-х лет. Опыт работы с Git. Опыт с микросервисной архитектурой.  Основной стек: Python 3.6+, FastAPI, Flask, MongoDB/ElasticSearch/Redis, RabbitMQ, Docker. Разработка и развитие backend проектов, разработка новых...</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>128627433</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Python-разработчик middle (FastAPI, AI/ML)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128627433</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3+ года коммерческой разработки на Python (опыт production-систем).  Практический опыт с FastAPI или аналогичными async-фреймворками (Starlette, aiohttp).   Развитие на пересечении backend и AI.  Возможность влиять на архитектурные решения.  Чистый код и инженерная культура (code review, автотесты, CI...</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>128677970</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Python разработчик</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128677970</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Что нужно уметь: Опыт разработки с использованием Python (Flask, FastAPI). Опыт проектирования и разработки REST API. Проектирование и оптимизация архитектуры... Сейчас активно расширяем функционал новыми модулями (аналитика, биллинг, обучение новых нейронок на собираемых данных).</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>128917430</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer (python)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128917430</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Опыт написания автотестов на python + pytest (backend) и playwright (ui). Уверенное владение sql. Понимание клиент-серверной архитектуры, http и... Разработка и поддержка автотестов для backend и ui (python, pytest, playwright). Проведение функционального, интеграционного и регрессионного тестирования. Приемка доработок внутренних...</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>127865214</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>160000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/127865214</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Разбираться в документации интегрируемых технологий. Ищем разработчик на python с опытом работы не менее 3х лет. Требуемые навыки: Умение... Работа с фреймворком FastApi. Поддержа существующей кодовой базы. Работа с фреймворком FastApi. Поддержа существующей кодовой базы.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>128677763</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Senior Python разработчик</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128677763</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сильного backend-разработчика: 5+ лет опыта на Python, глубокое знание асинхронного программирования (asyncio, FastAPI, SQLAlchemy). Опыт с Docker, Kubernetes... Разработка ядра backend-системы — микросервисы для обработки данных в реальном времени, интеграция с промышленными протоколами, API для аналитических сервисов. </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>129104674</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Middle Python Developer(Full Stack)/ Разработчик Telegram бота с AI-продуктом</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/129104674</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ты не джун, не «почти мидл», а зрелый Middle/ Middle+. Знаешь Django от миграций до middleware. Умеешь настраивать Celery +... Провести аудит проекта, оптимизацию кода и убрать все лишнее после ИИ агентов. Сделать документацию проекта. Корректно настроить БД и обращения...</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>128816653</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>240000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128816653</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Язык и фреймворки: уверенное владение Python, Django 5.0+, опыт работы с FastAPI. Базы данных: глубокие знания PostgreSQL (оптимизация... Строить эффективные SQL-запросы (включая сложные фильтры и джоины) и оптимизировать их через анализ планов запросов и приавильно использование индектов. </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>128842035</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128842035</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Опыт оптимизации производительности Python-приложений и работы с highload-системами. Глубокое понимание runtime-поведения Python-приложений. Навыки диагностики и устранения... Разработка и сопровождение backend-сервисов с ML-логикой. Оптимизация производительности и масштабируемости Python-приложений. Работа с реляционными и NoSQL базами...</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>128862578</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Senior/TeamLead Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128862578</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5+ лет коммерческой разработки на Python (backend), уверенный Senior-уровень;. Глубокое понимание принципов работы React на уровне middle.  Руководство отделом разработки. Ставить задачи, проводить code review, менторить middle-разработчиков. Проектировать и развивать backend-архитектуру платформы. Разрабатывать и поддерживать...</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>129066798</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Backend-разработчик (Python) Strong junior уровня</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ташкент</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/129066798</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Обязательные технические навыки. Python — уверенное владение языком, понимание ООП, базовых паттернов проектирования, чистого кода. PostgreSQL — уверенная работа с реляционной БД... Django — опыт разработки backend-приложений, работа с моделями, ORM, middleware, настройка проекта. Django REST Framework (DRF) — проектирование и реализация REST...</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>129022114</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/129022114</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые знания Python и желание развиваться в этом языке. Понимание принципов ООП и основ работы с веб-фреймворками (желательно Flask).  Разрабатывать и поддерживать веб-приложения на Python с использованием Flask. Участвовать в проектировании архитектуры и написании чистого, поддерживаемого кода. </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>128950131</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Middle (Python) Django backend Developer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ташкент</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128950131</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least 1 year of experience in Python Backend (Django) development. Knowledge of and hands-on experience with LangGraph.  Develop and maintain backend services using Python Backend (Django). Integrate and work with LangGraph. Optimize and refactor existing codebases. </t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>128880111</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Backend/Data Engineer (Python/FastAPI) — интеграции и обогащение данных</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128880111</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Уверенный Python 3.x и опыт разработки backend-сервисов (желательно FastAPI/Django и т.п.). Хороший SQL и опыт с... Разработать backend-сервис на Python/FastAPI (можем рассмотреть создание сервиса так же на Django): API-контракты, валидация, версии, идемпотентность. </t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Гибрид</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>128677448</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Back End разработчика (Python/Django)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ташкент</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128677448</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Высокий уровень владения Python с Django. Твёрдое понимание концепций и лучших практик разработки бэкенда. Опыт работы с системами баз данных... Разрабатывать и поддерживать высококачественные веб-приложения на Python с использованием Django. Сотрудничать с межфункциональными командами для проектирования и внедрения новых...</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>128844736</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Python разработчик</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128844736</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опыт работы с коммерческими проектами от 6-ти лет. Знания и опыт работы с Python, FastAPI, PostgreSQL, Kafka.  Писать новые и сопровождать текущие микросервисы на Python и FastAPI. Работать с PostgreSQL и Kafka. Производить код-ревью. </t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>128661064</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Стажер Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128661064</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Имеешь опыт разработки backend на Python 3.12. Знаешь и умеешь строить REST API с FastAPI. Имеешь навыки асинхронного программирования.  Разрабатывать новые сервисы. Дорабатывать функционал существующих сервисов. Писать unit-тесты и интеграционные тесты. Искать и исправлять баги. Вести документацию.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Гибрид</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>128661407</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Алматы</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128661407</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Знание Python. Условия: Опыт работы с: Backend фреймворками FastAPI/Django, реляционными базами данных, HTTP запросами, системы контроля версий Git.  Разработка и написание логики голосовых роботизированных помощников по скриптам коммуникации в мессенджерах, sms и т.п. с использованием собственных python...</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>128881788</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Python-разработчик/аналитик</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128881788</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Обязательно: - Python 3.13+: Глубокое знание новых функций (паттерн-матчинг улучшения асинхронного кода), оптимизация производительности через async/await и... Обработка и анализ данных. - Разработка API на FastAPI с генерацией отчетов. - Интеграция шаблонов Jinja с CSS/JS. FastAPI + Pydantic...</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>128446691</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128446691</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3+ лет коммерческой разработки на Python. Django / FastAPI / Flask — уверенные навыки с одним из фреймворков. Отличное понимание архитектуры веб... Разработка и поддержка backend-сервисов на Python. Проектирование и оптимизация архитектуры (модули, API, интеграции). Работа с БД: моделирование, оптимизация запросов...</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>128327084</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128327084</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опыт разработки на Python от 1 года. Знание основных фреймворков и библиотек Python. Умение работать с базами данных.  Разработка и поддержка backend-сервисов на Python. Интеграция с внешними и внутренними системами. Оптимизация и рефакторинг существующего кода. </t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>128708657</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Python/Php Backend Developer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128708657</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Базовые знания Python или Php. Опыт парсинга данных. Понимание RESTful API и взаимодействия с ними. Знание систем контроля версий, в... Разработка и поддержка серверной части веб-приложений с использованием Python/Php. Интеграция предварительно обученных моделей ИИ в продукты компании. </t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>129038908</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Middle+/Senior Python разработчик</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/129038908</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Опыт и технологии. Опыт коммерческой разработки на Python 3.8+ от 2 лет. Уверенное знание и практический опыт работы... Проект: Разработка функциональности для проекта BI. Создание и поддержка REST API. Работа с моделями, ORM, миграциями. Аутентификация и авторизация (JWT...</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>128913758</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Python разработчик (Junior)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128913758</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Знание Python, SQL и Git. Умение работать с библиотеками для разработки ботов в Telegram(aiogram/pyTelegramBotAPI/Pyrogram) или в ВК... Разработка ботов, на языке Python для Telegram и ВК. Создание скриптов для автоматизации бизнес-процессов. Проектирование и разработка бэкенда для...</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/vacancies.xlsx
+++ b/data/vacancies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,6 +1952,158 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>128754739</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Python Developer / Backend (парсеры)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>160000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128754739</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Опыт работы с парсерами на Python от 1 года. Знание Playwright, selenium, Httpx, requests и подобные. Rabbit / redis приветствуются.  Разработка Backend микросервисов и сервисов. Проектирование новых сервисов, участие в разработке очень масштабной внутренней инфраструктуры проектов. Поддержка существующих сервисов и...</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>128631830</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AL/ML/Prompt engineer (Python, GPT, LLaMA, Claude, open-source LLM)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128631830</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Уверенное знание Python (asyncio, typing, dataclasses). Опыт работы с PyTorch/Transformers/vLLM. Опыт тонкой настройки и дообучения LLM.  Создание и дообучение моделей для работы с изображениями, текстом и аудио. Точечное дообучение LLM под специализированные задачи. Разработка и развёртывание...</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>128900119</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Инженер-программист С/С++/Python</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128900119</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>знание языков программирования C/C++, дополнительно приветствуется Python. - знание и опыт использования интерфейсов I2C, UART, CAN, Ethernet, 1... ...постоянной основе, в команду разработчиков требуется Инженер-программист С/С++/Python, разработчик встроенного программного обеспечения устройств на базе микроконтроллеров на...</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>128782116</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Python Engineer (senior)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>225000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://hh.ru/vacancy/128782116</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Знание FastAPI, Flask, Django или других популярных Python-фреймворков. Опыт профилирования и оптимизации Python-кода. Опыт написания CLI-инструментов.  Разработка и поддержка модулей и сервисов на Python. Рефакторинг и оптимизация существующего кода для повышения производительности и читаемости. </t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>На месте работодателя</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/vacancies.xlsx
+++ b/data/vacancies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,120 +505,6 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Не определён</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>128631830</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AL/ML/Prompt engineer (Python, GPT, LLaMA, Claude, open-source LLM)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://hh.ru/vacancy/128631830</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Уверенное знание Python (asyncio, typing, dataclasses). Опыт работы с PyTorch/Transformers/vLLM. Опыт тонкой настройки и дообучения LLM.  Создание и дообучение моделей для работы с изображениями, текстом и аудио. Точечное дообучение LLM под специализированные задачи. Разработка и развёртывание...</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>128900119</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Инженер-программист С/С++/Python</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9999999</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://hh.ru/vacancy/128900119</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>знание языков программирования C/C++, дополнительно приветствуется Python. - знание и опыт использования интерфейсов I2C, UART, CAN, Ethernet, 1... ...постоянной основе, в команду разработчиков требуется Инженер-программист С/С++/Python, разработчик встроенного программного обеспечения устройств на базе микроконтроллеров на...</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>На месте работодателя</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>128782116</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Python Engineer (senior)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9999999</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://hh.ru/vacancy/128782116</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Знание FastAPI, Flask, Django или других популярных Python-фреймворков. Опыт профилирования и оптимизации Python-кода. Опыт написания CLI-инструментов.  Разработка и поддержка модулей и сервисов на Python. Рефакторинг и оптимизация существующего кода для повышения производительности и читаемости. </t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>На месте работодателя</t>
         </is>
       </c>
     </row>
